--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513253_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513253_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3846</v>
+        <v>1.8427</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5556</v>
+        <v>6.3308</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.171</v>
+        <v>-4.4881</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6172</v>
@@ -610,13 +610,13 @@
         <v>0.8811</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7992</v>
+        <v>0.2574</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3465</v>
+        <v>0.1217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4527</v>
+        <v>0.1356</v>
       </c>
       <c r="V2" t="n">
         <v>2.4228</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.2786</v>
+        <v>-1.4549</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1187</v>
+        <v>-1.3345</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.16</v>
+        <v>-0.1204</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.7381</v>
+        <v>-1.7169</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6539</v>
+        <v>-1.106</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0842</v>
+        <v>-0.6109</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.5062</v>
+        <v>-0.6615</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7631</v>
+        <v>-0.6995</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7431</v>
+        <v>0.038</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2319</v>
+        <v>-1.0554</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1092</v>
+        <v>-0.4065</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3411</v>
+        <v>-0.6489</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.7622</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2203</v>
+        <v>-2.2027</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2203</v>
+        <v>0.4405</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3405</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4889</v>
+        <v>0.4108</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1484</v>
+        <v>0.1199</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1189</v>
+        <v>1.4934</v>
       </c>
       <c r="W3" t="n">
         <v>1.1189</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.48</v>
+        <v>-1.7473</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1002</v>
+        <v>-0.5873</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3799</v>
+        <v>-1.16</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7169</v>
+        <v>-2.7381</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.106</v>
+        <v>-0.6539</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6109</v>
+        <v>-2.0842</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6615</v>
+        <v>-1.5062</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6995</v>
+        <v>-0.7631</v>
       </c>
       <c r="L4" t="n">
-        <v>0.038</v>
+        <v>-0.7431</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0554</v>
+        <v>-1.2319</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4065</v>
+        <v>0.1092</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6489</v>
+        <v>-1.3411</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7622</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2027</v>
+        <v>-0.2203</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4405</v>
+        <v>0.2203</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5056</v>
+        <v>-0.1281</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6451</v>
+        <v>0.0203</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1395</v>
+        <v>-0.1484</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4934</v>
+        <v>1.1189</v>
       </c>
       <c r="W4" t="n">
         <v>1.1189</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6729</v>
+        <v>-1.8376</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5659</v>
+        <v>0.7471</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2388</v>
+        <v>-2.5847</v>
       </c>
       <c r="G5" t="n">
         <v>-1.75</v>
@@ -844,13 +844,13 @@
         <v>0.8811</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1256</v>
+        <v>-0.0391</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4562</v>
+        <v>-0.275</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5819</v>
+        <v>0.236</v>
       </c>
       <c r="V5" t="n">
         <v>1.4934</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5014</v>
+        <v>-2.3806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2271</v>
+        <v>0.5786</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7285</v>
+        <v>-2.9591</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0339</v>
@@ -922,13 +922,13 @@
         <v>0.4405</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2947</v>
+        <v>0.4155</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6765</v>
+        <v>-0.325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9712</v>
+        <v>0.7406</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5356</v>
+        <v>-2.503</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8641</v>
+        <v>-2.6298</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3285</v>
+        <v>0.1267</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1057</v>
@@ -1000,13 +1000,13 @@
         <v>0.4405</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1295</v>
+        <v>0.1621</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7046</v>
+        <v>-0.4703</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.6324</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6699</v>
+        <v>-2.9963</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4175</v>
+        <v>0.8317</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.0874</v>
+        <v>-3.8279</v>
       </c>
       <c r="G8" t="n">
         <v>-3.8685</v>
@@ -1078,13 +1078,13 @@
         <v>0.8811</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0665</v>
+        <v>0.7401</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7216</v>
+        <v>0.1358</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3449</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7489</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3161</v>
+        <v>-3.6708</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.701</v>
+        <v>-0.9981</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6151</v>
+        <v>-2.6727</v>
       </c>
       <c r="G9" t="n">
         <v>-4.5802</v>
@@ -1156,13 +1156,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5992</v>
+        <v>0.0461</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0608</v>
+        <v>-0.3579</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4616</v>
+        <v>0.4039</v>
       </c>
       <c r="V9" t="n">
         <v>1.3039</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6684</v>
+        <v>-4.343</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2869</v>
+        <v>-1.1057</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3814</v>
+        <v>-3.2373</v>
       </c>
       <c r="G10" t="n">
         <v>-3.005</v>
@@ -1234,13 +1234,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.985</v>
+        <v>-0.6597</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7687</v>
+        <v>-0.5874</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2164</v>
+        <v>-0.0722</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1189</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2703</v>
+        <v>-4.6074</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6352</v>
+        <v>-1.5498</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6351</v>
+        <v>-3.0576</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0127</v>
+        <v>-3.3443</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1474</v>
+        <v>-1.5553</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8653</v>
+        <v>-1.789</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2416</v>
+        <v>-1.2857</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7175</v>
+        <v>-1.5083</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5242</v>
+        <v>0.2225</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.771</v>
+        <v>-2.0586</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.43</v>
+        <v>-0.047</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3411</v>
+        <v>-2.0116</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8811</v>
+        <v>0.4405</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3216</v>
+        <v>-0.2203</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4405</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3765</v>
+        <v>-0.5847</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0438</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3046</v>
+        <v>-0.5409</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2842</v>
+        <v>-5.2703</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0825</v>
+        <v>-3.6352</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2017</v>
+        <v>-1.6351</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3443</v>
+        <v>-4.0127</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5553</v>
+        <v>-1.1474</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.789</v>
+        <v>-2.8653</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2857</v>
+        <v>-2.2416</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5083</v>
+        <v>-0.7175</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2225</v>
+        <v>-1.5242</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0586</v>
+        <v>-1.771</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.047</v>
+        <v>-0.43</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0116</v>
+        <v>-1.3411</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.8811</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.3216</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.4405</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-0.2203</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.6608000000000001</v>
-      </c>
       <c r="S12" t="n">
-        <v>-1.2615</v>
+        <v>-0.3765</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5765</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3046</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.967</v>
+        <v>-9.9712</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.402</v>
+        <v>-5.7521</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.565</v>
+        <v>-4.2191</v>
       </c>
       <c r="G13" t="n">
         <v>-8.972</v>
@@ -1468,13 +1468,13 @@
         <v>1.1014</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0786</v>
+        <v>-0.0828</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0046</v>
+        <v>-0.3548</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.074</v>
+        <v>0.2719</v>
       </c>
       <c r="V13" t="n">
         <v>0.185</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.2598</v>
+        <v>-38.9397</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.4245</v>
+        <v>-9.1043</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.8354</v>
+        <v>-29.8353</v>
       </c>
       <c r="G14" t="n">
         <v>-38.7445</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.6933</v>
+        <v>-7.693300000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-31.05110000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4733</v>
+        <v>-2.473300000000001</v>
       </c>
       <c r="K14" t="n">
         <v>-3.9396</v>
@@ -1546,13 +1546,13 @@
         <v>7.7094</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.03919999999999968</v>
+        <v>0.281</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.1177</v>
+        <v>-1.7975</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0786</v>
+        <v>2.078499999999999</v>
       </c>
       <c r="V14" t="n">
         <v>5.0307</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.0337</v>
+        <v>9.634399999999999</v>
       </c>
       <c r="E15" t="n">
         <v>7.7634</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2703</v>
+        <v>1.871</v>
       </c>
       <c r="G15" t="n">
         <v>10.5475</v>
@@ -1624,13 +1624,13 @@
         <v>1.5419</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.853</v>
+        <v>-0.2523</v>
       </c>
       <c r="T15" t="n">
         <v>-0.9046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0516</v>
+        <v>0.6523</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6086</v>
+        <v>6.1843</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9574</v>
+        <v>5.3042</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6512</v>
+        <v>0.8801</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9563</v>
+        <v>7.0041</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4922</v>
+        <v>1.052</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4642</v>
+        <v>5.9521</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3868</v>
+        <v>6.1863</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1176</v>
+        <v>0.8807</v>
       </c>
       <c r="L16" t="n">
-        <v>4.2693</v>
+        <v>5.3056</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4305</v>
+        <v>0.8179</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3746</v>
+        <v>0.1714</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8051</v>
+        <v>0.6465</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5419</v>
+        <v>-0.2203</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.3216</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5419</v>
+        <v>1.1014</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1103</v>
+        <v>0.3343</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5484</v>
+        <v>0.2546</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6587</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9339</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1189</v>
+        <v>0.185</v>
       </c>
       <c r="X16" t="n">
         <v>-1.1189</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3251</v>
+        <v>5.6904</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6012</v>
+        <v>4.9574</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7238</v>
+        <v>0.733</v>
       </c>
       <c r="G17" t="n">
-        <v>7.0041</v>
+        <v>3.9563</v>
       </c>
       <c r="H17" t="n">
-        <v>1.052</v>
+        <v>0.4922</v>
       </c>
       <c r="I17" t="n">
-        <v>5.9521</v>
+        <v>3.4642</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1863</v>
+        <v>4.3868</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8807</v>
+        <v>0.1176</v>
       </c>
       <c r="L17" t="n">
-        <v>5.3056</v>
+        <v>4.2693</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8179</v>
+        <v>-0.4305</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1714</v>
+        <v>0.3746</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6465</v>
+        <v>-0.8051</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2203</v>
+        <v>1.5419</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3216</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1014</v>
+        <v>1.5419</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5249</v>
+        <v>0.1922</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4484</v>
+        <v>-0.5484</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0765</v>
+        <v>0.7406</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9339</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.185</v>
+        <v>1.1189</v>
       </c>
       <c r="X17" t="n">
         <v>-1.1189</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4821</v>
+        <v>4.8978</v>
       </c>
       <c r="E18" t="n">
         <v>3.5416</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9406</v>
+        <v>1.3562</v>
       </c>
       <c r="G18" t="n">
         <v>4.7765</v>
@@ -1858,13 +1858,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1754</v>
+        <v>0.2402</v>
       </c>
       <c r="T18" t="n">
         <v>0.2046</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.38</v>
+        <v>0.0356</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5595</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2923</v>
+        <v>4.681</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5674</v>
+        <v>3.6845</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7249</v>
+        <v>0.9964</v>
       </c>
       <c r="G19" t="n">
         <v>3.052</v>
@@ -1936,13 +1936,13 @@
         <v>1.1014</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0153</v>
+        <v>0.3734</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2967</v>
+        <v>0.4139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.312</v>
+        <v>-0.0405</v>
       </c>
       <c r="V19" t="n">
         <v>0.3745</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3652</v>
+        <v>2.9693</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3102</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9449</v>
+        <v>2.0978</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0575</v>
+        <v>2.6586</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9866</v>
+        <v>0.2336</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0709</v>
+        <v>2.425</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5553</v>
+        <v>3.0707</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4558</v>
+        <v>-0.0704</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0996</v>
+        <v>3.1412</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4978</v>
+        <v>-0.4121</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5308</v>
+        <v>0.3041</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0286</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5419</v>
+        <v>0.8811</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5419</v>
+        <v>1.9825</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5558</v>
+        <v>-0.0109</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8046</v>
+        <v>-0.7234</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2488</v>
+        <v>0.7125</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6784</v>
+        <v>-0.5595</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5595</v>
+        <v>-0.3745</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2378</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3091</v>
+        <v>2.793</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7543</v>
+        <v>3.3102</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5548</v>
+        <v>-0.5172</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6586</v>
+        <v>3.0575</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2336</v>
+        <v>1.9866</v>
       </c>
       <c r="I21" t="n">
-        <v>2.425</v>
+        <v>1.0709</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0707</v>
+        <v>3.5553</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0704</v>
+        <v>1.4558</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1412</v>
+        <v>2.0996</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4121</v>
+        <v>-0.4978</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3041</v>
+        <v>0.5308</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-1.0286</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8811</v>
+        <v>1.5419</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9825</v>
+        <v>1.5419</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6711</v>
+        <v>-0.1281</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8406</v>
+        <v>-0.8046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1694</v>
+        <v>0.6765</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5595</v>
+        <v>-1.6784</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3745</v>
+        <v>0.5595</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.185</v>
+        <v>-2.2378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.1792</v>
+        <v>1.7179</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7593</v>
+        <v>-0.9291</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4199</v>
+        <v>2.647</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7503</v>
+        <v>0.426</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6313</v>
+        <v>-0.2585</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8811</v>
+        <v>0.6845</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0292</v>
+        <v>-0.5514</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7254</v>
+        <v>-0.9691</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3038</v>
+        <v>0.4177</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2789</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.094</v>
+        <v>0.7106</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1848</v>
+        <v>0.2668</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R22" t="n">
         <v>1.1014</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2615</v>
+        <v>0.173</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1046</v>
+        <v>-0.3953</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1569</v>
+        <v>0.5683</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9339</v>
+        <v>1.1189</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3745</v>
+        <v>1.1189</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6902</v>
+        <v>1.6362</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1466</v>
+        <v>0.0877</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8368</v>
+        <v>1.5486</v>
       </c>
       <c r="G23" t="n">
         <v>1.2339</v>
@@ -2248,13 +2248,13 @@
         <v>0.2203</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4562</v>
+        <v>0.4023</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2281</v>
+        <v>0.0062</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6843</v>
+        <v>0.3961</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.3748</v>
+        <v>1.4344</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0463</v>
+        <v>1.2906</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4211</v>
+        <v>0.1438</v>
       </c>
       <c r="G24" t="n">
-        <v>0.426</v>
+        <v>0.7503</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2585</v>
+        <v>1.6313</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6845</v>
+        <v>-0.8811</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5514</v>
+        <v>2.0292</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9691</v>
+        <v>1.7254</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4177</v>
+        <v>0.3038</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9772999999999999</v>
+        <v>-1.2789</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7106</v>
+        <v>-0.094</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2668</v>
+        <v>-1.1848</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.1014</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>1.1014</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1701</v>
+        <v>0.5167</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5124</v>
+        <v>-0.3641</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3424</v>
+        <v>0.8808</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1189</v>
+        <v>-0.9339</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1189</v>
+        <v>-0.3745</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="25">
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2343</v>
+        <v>0.2211</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2685</v>
+        <v>0.6552</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5028</v>
+        <v>-0.4341</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6501</v>
+        <v>1.6621</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5788</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9286</v>
+        <v>1.6621</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4464</v>
+        <v>1.6691</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.7502</v>
+        <v>0.1176</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3038</v>
+        <v>1.5516</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7962</v>
+        <v>-0.007</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1714</v>
+        <v>-0.1176</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6249</v>
+        <v>0.1106</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2203</v>
+        <v>-0.2203</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2203</v>
+        <v>-1.1014</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4405</v>
+        <v>0.8811</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2191</v>
+        <v>0.0832</v>
       </c>
       <c r="T26" t="n">
-        <v>1.3981</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.179</v>
+        <v>-0.0042</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.555</v>
+        <v>-1.3039</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.555</v>
+        <v>-1.3039</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0956</v>
+        <v>-0.5263</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7724</v>
+        <v>-0.9715</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6768</v>
+        <v>0.4452</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6621</v>
+        <v>-0.6501</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-1.5788</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6621</v>
+        <v>0.9286</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6691</v>
+        <v>-1.4464</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1176</v>
+        <v>-1.7502</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5516</v>
+        <v>0.3038</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.007</v>
+        <v>0.7962</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1176</v>
+        <v>0.1714</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1106</v>
+        <v>0.6249</v>
       </c>
       <c r="P27" t="n">
+        <v>0.2203</v>
+      </c>
+      <c r="Q27" t="n">
         <v>-0.2203</v>
       </c>
-      <c r="Q27" t="n">
-        <v>-1.1014</v>
-      </c>
       <c r="R27" t="n">
-        <v>0.8811</v>
+        <v>0.4405</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0424</v>
+        <v>0.4585</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2046</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2469</v>
+        <v>-0.2366</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.3039</v>
+        <v>-0.555</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.3039</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>39.25979999999999</v>
+        <v>41.6031</v>
       </c>
       <c r="E28" t="n">
-        <v>29.83540000000001</v>
+        <v>29.8353</v>
       </c>
       <c r="F28" t="n">
-        <v>9.424500000000002</v>
+        <v>11.7678</v>
       </c>
       <c r="G28" t="n">
         <v>38.7443</v>
@@ -2623,7 +2623,7 @@
         <v>2.4733</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9395</v>
+        <v>3.939500000000001</v>
       </c>
       <c r="O28" t="n">
         <v>-1.4658</v>
@@ -2638,13 +2638,13 @@
         <v>13.2165</v>
       </c>
       <c r="S28" t="n">
-        <v>0.03910000000000013</v>
+        <v>2.3825</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.0785</v>
+        <v>-2.0786</v>
       </c>
       <c r="U28" t="n">
-        <v>2.1177</v>
+        <v>4.4611</v>
       </c>
       <c r="V28" t="n">
         <v>-5.0307</v>
